--- a/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigD4_5_mechanism_specificity_source_data.xlsx
+++ b/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigD4_5_mechanism_specificity_source_data.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,25 +459,35 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>n_process_time_blocks</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>bootstrap_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>target</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>required_for_acceptance</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>interpretation</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>calibration_id</t>
         </is>
@@ -498,28 +508,36 @@
         <v>0.889424288233812</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8468049256739733</v>
+        <v>0.8568393473265207</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9257243638196019</v>
+        <v>0.925209311510676</v>
       </c>
       <c r="F2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
         <v>0.7</v>
       </c>
-      <c r="G2" t="b">
+      <c r="I2" t="b">
         <v>1</v>
       </c>
-      <c r="H2" t="b">
+      <c r="J2" t="b">
         <v>1</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>internal chronological-holdout stress test</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -538,28 +556,36 @@
         <v>0.8763542454018645</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8351843978332074</v>
+        <v>0.8417177514517648</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9134086041824137</v>
+        <v>0.9154229243202758</v>
       </c>
       <c r="F3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>0.7</v>
       </c>
-      <c r="G3" t="b">
+      <c r="I3" t="b">
         <v>1</v>
       </c>
-      <c r="H3" t="b">
+      <c r="J3" t="b">
         <v>1</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>internal chronological-holdout stress test</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -578,28 +604,36 @@
         <v>0.7312925170068028</v>
       </c>
       <c r="D4" t="n">
-        <v>0.684311224489796</v>
+        <v>0.6812496943382595</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7864355001259763</v>
+        <v>0.7920538067799162</v>
       </c>
       <c r="F4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>0.7</v>
       </c>
-      <c r="G4" t="b">
+      <c r="I4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" t="b">
+      <c r="J4" t="b">
         <v>1</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>internal chronological-holdout stress test</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -618,28 +652,36 @@
         <v>0.5726568405139834</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5591592655580752</v>
+        <v>0.5581598767644493</v>
       </c>
       <c r="E5" t="n">
-        <v>0.595472726127488</v>
+        <v>0.5946279839174262</v>
       </c>
       <c r="F5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>0.7</v>
       </c>
-      <c r="G5" t="b">
+      <c r="I5" t="b">
         <v>0</v>
       </c>
-      <c r="H5" t="b">
+      <c r="J5" t="b">
         <v>0</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>secondary sensitivity only; isolated spikes remain a D1 responsibility</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -661,25 +703,33 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03947368421052631</v>
+        <v>0.04</v>
       </c>
       <c r="F6" t="n">
+        <v>11</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>0.1</v>
       </c>
-      <c r="G6" t="b">
+      <c r="I6" t="b">
         <v>1</v>
       </c>
-      <c r="H6" t="b">
+      <c r="J6" t="b">
         <v>1</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>paired conditional FAR among windows that were non-alarming before injection</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -704,22 +754,30 @@
         <v>0.03947368421052631</v>
       </c>
       <c r="F7" t="n">
+        <v>11</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
         <v>0.1</v>
       </c>
-      <c r="G7" t="b">
+      <c r="I7" t="b">
         <v>1</v>
       </c>
-      <c r="H7" t="b">
+      <c r="J7" t="b">
         <v>1</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>paired conditional FAR among windows that were non-alarming before injection</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -793,7 +851,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -819,7 +877,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -845,7 +903,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -871,7 +929,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -897,7 +955,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -923,7 +981,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -949,7 +1007,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -975,7 +1033,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1059,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1085,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1111,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1137,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1163,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1189,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1215,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1241,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1267,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1293,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1319,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1345,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1371,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1397,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1423,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1449,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1475,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1501,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1527,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1553,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1579,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1605,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1631,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1657,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1683,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1709,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1735,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1761,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1787,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1813,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1839,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1865,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1891,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1917,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1943,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1969,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1995,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1963,7 +2021,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -1989,7 +2047,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2073,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2099,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2125,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2151,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2177,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2203,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2229,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2255,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2281,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2307,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2333,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2359,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2385,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2411,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2437,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2463,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2489,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2515,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2541,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2567,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2593,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2619,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2645,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2671,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2697,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2723,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2749,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2775,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2801,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2827,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2853,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2879,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2905,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2931,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2957,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2983,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2951,7 +3009,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -2977,7 +3035,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3061,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3087,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3113,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3139,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3165,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3191,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3217,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3185,7 +3243,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3269,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3295,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3321,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3347,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3373,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3399,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3425,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3451,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3477,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3445,7 +3503,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3529,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3555,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3581,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3549,7 +3607,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3633,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3659,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3627,7 +3685,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3653,7 +3711,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3737,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3763,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3789,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3815,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3841,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3867,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3893,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3919,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3887,7 +3945,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3913,7 +3971,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3997,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3965,7 +4023,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -3991,7 +4049,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4075,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4101,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4069,7 +4127,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4095,7 +4153,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4179,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4205,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4173,7 +4231,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4257,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4283,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4309,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4335,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4303,7 +4361,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4387,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4355,7 +4413,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4381,7 +4439,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4407,7 +4465,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4491,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4517,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4485,7 +4543,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4569,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4537,7 +4595,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4621,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4589,7 +4647,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4615,7 +4673,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4699,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4725,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4693,7 +4751,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4777,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4803,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4771,7 +4829,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4797,7 +4855,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4823,7 +4881,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4907,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4875,7 +4933,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4959,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4985,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4953,7 +5011,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -4979,7 +5037,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5005,7 +5063,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5089,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5115,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5141,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5167,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5193,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5161,7 +5219,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5245,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5213,7 +5271,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5239,7 +5297,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5265,7 +5323,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5291,7 +5349,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5375,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5401,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5369,7 +5427,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5395,7 +5453,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5479,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5447,7 +5505,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5473,7 +5531,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5557,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5525,7 +5583,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5609,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5577,7 +5635,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5603,7 +5661,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5687,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5713,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5739,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5707,7 +5765,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5733,7 +5791,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5759,7 +5817,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5785,7 +5843,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5811,7 +5869,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5837,7 +5895,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5919,7 @@
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5947,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5915,7 +5973,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5941,7 +5999,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5967,7 +6025,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -5993,7 +6051,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6019,7 +6077,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6103,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6071,7 +6129,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6097,7 +6155,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6181,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6149,7 +6207,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6233,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6259,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6285,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6311,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6279,7 +6337,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6305,7 +6363,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6331,7 +6389,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6415,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6441,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6467,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6493,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6519,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6487,7 +6545,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6571,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6539,7 +6597,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6565,7 +6623,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6649,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6617,7 +6675,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6643,7 +6701,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6669,7 +6727,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6695,7 +6753,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6721,7 +6779,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6747,7 +6805,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6773,7 +6831,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6799,7 +6857,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6883,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6909,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6935,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6961,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6929,7 +6987,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6955,7 +7013,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -6981,7 +7039,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7007,7 +7065,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7033,7 +7091,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7117,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7085,7 +7143,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7169,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7137,7 +7195,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7221,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7189,7 +7247,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7215,7 +7273,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7241,7 +7299,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7267,7 +7325,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7351,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7319,7 +7377,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7345,7 +7403,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7429,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7397,7 +7455,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7423,7 +7481,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7449,7 +7507,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7475,7 +7533,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7501,7 +7559,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7585,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7553,7 +7611,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7579,7 +7637,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7605,7 +7663,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7631,7 +7689,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7715,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7683,7 +7741,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7767,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7735,7 +7793,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7819,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7787,7 +7845,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7813,7 +7871,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7839,7 +7897,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7865,7 +7923,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7891,7 +7949,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7917,7 +7975,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7943,7 +8001,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7969,7 +8027,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -7995,7 +8053,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8079,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8047,7 +8105,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8073,7 +8131,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8099,7 +8157,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8125,7 +8183,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8151,7 +8209,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8177,7 +8235,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8261,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8287,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8255,7 +8313,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8339,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8307,7 +8365,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8333,7 +8391,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8359,7 +8417,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8385,7 +8443,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8411,7 +8469,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8437,7 +8495,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8463,7 +8521,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8489,7 +8547,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8515,7 +8573,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8541,7 +8599,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8567,7 +8625,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8593,7 +8651,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8619,7 +8677,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8703,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8671,7 +8729,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8755,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8723,7 +8781,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8807,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8775,7 +8833,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8801,7 +8859,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8885,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8853,7 +8911,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8879,7 +8937,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8905,7 +8963,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8989,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8957,7 +9015,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -8983,7 +9041,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9009,7 +9067,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9035,7 +9093,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9061,7 +9119,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9145,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9113,7 +9171,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9139,7 +9197,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9165,7 +9223,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9191,7 +9249,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9275,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9243,7 +9301,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9269,7 +9327,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9295,7 +9353,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9379,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9405,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9373,7 +9431,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9399,7 +9457,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9425,7 +9483,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9451,7 +9509,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9477,7 +9535,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9503,7 +9561,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9587,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9555,7 +9613,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9581,7 +9639,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9607,7 +9665,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9691,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9659,7 +9717,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9685,7 +9743,7 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9711,7 +9769,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9737,7 +9795,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9763,7 +9821,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9789,7 +9847,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9815,7 +9873,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9841,7 +9899,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9925,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9951,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9919,7 +9977,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9945,7 +10003,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9971,7 +10029,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -9997,7 +10055,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10023,7 +10081,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10049,7 +10107,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10075,7 +10133,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10101,7 +10159,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10127,7 +10185,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10211,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10179,7 +10237,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10263,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10231,7 +10289,7 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10257,7 +10315,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10341,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10309,7 +10367,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10335,7 +10393,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10361,7 +10419,7 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10387,7 +10445,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10413,7 +10471,7 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10439,7 +10497,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10465,7 +10523,7 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10549,7 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10517,7 +10575,7 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10543,7 +10601,7 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10569,7 +10627,7 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10595,7 +10653,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10621,7 +10679,7 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10647,7 +10705,7 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10673,7 +10731,7 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10757,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10725,7 +10783,7 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10751,7 +10809,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10777,7 +10835,7 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10803,7 +10861,7 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10829,7 +10887,7 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10913,7 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10881,7 +10939,7 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10907,7 +10965,7 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10933,7 +10991,7 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10959,7 +11017,7 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -10985,7 +11043,7 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11011,7 +11069,7 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11037,7 +11095,7 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11061,7 +11119,7 @@
       <c r="E397" t="inlineStr"/>
       <c r="F397" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11089,7 +11147,7 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11115,7 +11173,7 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11141,7 +11199,7 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11167,7 +11225,7 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11193,7 +11251,7 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11219,7 +11277,7 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11245,7 +11303,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11271,7 +11329,7 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11355,7 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11323,7 +11381,7 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11349,7 +11407,7 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11375,7 +11433,7 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11401,7 +11459,7 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11427,7 +11485,7 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11453,7 +11511,7 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11537,7 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11505,7 +11563,7 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11589,7 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11557,7 +11615,7 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11583,7 +11641,7 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11667,7 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11635,7 +11693,7 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11661,7 +11719,7 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11687,7 +11745,7 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11713,7 +11771,7 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11797,7 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11765,7 +11823,7 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11791,7 +11849,7 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11817,7 +11875,7 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11843,7 +11901,7 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11869,7 +11927,7 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11953,7 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11921,7 +11979,7 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11947,7 +12005,7 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11973,7 +12031,7 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -11999,7 +12057,7 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12025,7 +12083,7 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12051,7 +12109,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12077,7 +12135,7 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12103,7 +12161,7 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12129,7 +12187,7 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12155,7 +12213,7 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12181,7 +12239,7 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12207,7 +12265,7 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12233,7 +12291,7 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12259,7 +12317,7 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12285,7 +12343,7 @@
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12311,7 +12369,7 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12337,7 +12395,7 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12363,7 +12421,7 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12389,7 +12447,7 @@
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12415,7 +12473,7 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12441,7 +12499,7 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12467,7 +12525,7 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12493,7 +12551,7 @@
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12519,7 +12577,7 @@
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12545,7 +12603,7 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12571,7 +12629,7 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12597,7 +12655,7 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12623,7 +12681,7 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12649,7 +12707,7 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12675,7 +12733,7 @@
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12701,7 +12759,7 @@
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12727,7 +12785,7 @@
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12753,7 +12811,7 @@
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12779,7 +12837,7 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12805,7 +12863,7 @@
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12831,7 +12889,7 @@
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12857,7 +12915,7 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12883,7 +12941,7 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12909,7 +12967,7 @@
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12935,7 +12993,7 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12961,7 +13019,7 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -12987,7 +13045,7 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13013,7 +13071,7 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13039,7 +13097,7 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13065,7 +13123,7 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13149,7 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13117,7 +13175,7 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13201,7 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13169,7 +13227,7 @@
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13195,7 +13253,7 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13221,7 +13279,7 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13247,7 +13305,7 @@
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13273,7 +13331,7 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13299,7 +13357,7 @@
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13325,7 +13383,7 @@
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13351,7 +13409,7 @@
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13377,7 +13435,7 @@
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13403,7 +13461,7 @@
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13429,7 +13487,7 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13455,7 +13513,7 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13481,7 +13539,7 @@
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13507,7 +13565,7 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13533,7 +13591,7 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13559,7 +13617,7 @@
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13585,7 +13643,7 @@
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13611,7 +13669,7 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13637,7 +13695,7 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13663,7 +13721,7 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13689,7 +13747,7 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13715,7 +13773,7 @@
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13741,7 +13799,7 @@
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13767,7 +13825,7 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13793,7 +13851,7 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13819,7 +13877,7 @@
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13845,7 +13903,7 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13871,7 +13929,7 @@
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13897,7 +13955,7 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13923,7 +13981,7 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13949,7 +14007,7 @@
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -13975,7 +14033,7 @@
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14001,7 +14059,7 @@
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14027,7 +14085,7 @@
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14053,7 +14111,7 @@
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14079,7 +14137,7 @@
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14105,7 +14163,7 @@
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14131,7 +14189,7 @@
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14157,7 +14215,7 @@
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14183,7 +14241,7 @@
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14209,7 +14267,7 @@
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14235,7 +14293,7 @@
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14261,7 +14319,7 @@
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14287,7 +14345,7 @@
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14313,7 +14371,7 @@
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14339,7 +14397,7 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14365,7 +14423,7 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14449,7 @@
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14417,7 +14475,7 @@
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14443,7 +14501,7 @@
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14469,7 +14527,7 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14495,7 +14553,7 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14521,7 +14579,7 @@
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14605,7 @@
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14573,7 +14631,7 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14599,7 +14657,7 @@
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14625,7 +14683,7 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14651,7 +14709,7 @@
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14677,7 +14735,7 @@
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14703,7 +14761,7 @@
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14729,7 +14787,7 @@
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14755,7 +14813,7 @@
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14781,7 +14839,7 @@
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14807,7 +14865,7 @@
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14891,7 @@
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14859,7 +14917,7 @@
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14885,7 +14943,7 @@
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14911,7 +14969,7 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14937,7 +14995,7 @@
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14963,7 +15021,7 @@
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -14989,7 +15047,7 @@
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15015,7 +15073,7 @@
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15041,7 +15099,7 @@
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15067,7 +15125,7 @@
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15151,7 @@
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15119,7 +15177,7 @@
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15145,7 +15203,7 @@
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15171,7 +15229,7 @@
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15197,7 +15255,7 @@
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15223,7 +15281,7 @@
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15249,7 +15307,7 @@
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15275,7 +15333,7 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15301,7 +15359,7 @@
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15327,7 +15385,7 @@
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15353,7 +15411,7 @@
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15379,7 +15437,7 @@
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15405,7 +15463,7 @@
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15431,7 +15489,7 @@
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15457,7 +15515,7 @@
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15483,7 +15541,7 @@
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15509,7 +15567,7 @@
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15535,7 +15593,7 @@
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15561,7 +15619,7 @@
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15587,7 +15645,7 @@
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15613,7 +15671,7 @@
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15639,7 +15697,7 @@
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15665,7 +15723,7 @@
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15691,7 +15749,7 @@
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15717,7 +15775,7 @@
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15743,7 +15801,7 @@
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15769,7 +15827,7 @@
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15795,7 +15853,7 @@
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15821,7 +15879,7 @@
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15847,7 +15905,7 @@
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15873,7 +15931,7 @@
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15899,7 +15957,7 @@
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15925,7 +15983,7 @@
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15951,7 +16009,7 @@
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -15977,7 +16035,7 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16003,7 +16061,7 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16029,7 +16087,7 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16055,7 +16113,7 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16081,7 +16139,7 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16107,7 +16165,7 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16191,7 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16159,7 +16217,7 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16185,7 +16243,7 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16211,7 +16269,7 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16237,7 +16295,7 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16263,7 +16321,7 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16287,7 +16345,7 @@
       <c r="E598" t="inlineStr"/>
       <c r="F598" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16315,7 +16373,7 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16341,7 +16399,7 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16367,7 +16425,7 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16393,7 +16451,7 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16419,7 +16477,7 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16445,7 +16503,7 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16471,7 +16529,7 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16497,7 +16555,7 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16523,7 +16581,7 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16549,7 +16607,7 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16575,7 +16633,7 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16601,7 +16659,7 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16627,7 +16685,7 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16653,7 +16711,7 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16679,7 +16737,7 @@
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16705,7 +16763,7 @@
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16731,7 +16789,7 @@
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16757,7 +16815,7 @@
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16783,7 +16841,7 @@
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16809,7 +16867,7 @@
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16835,7 +16893,7 @@
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16861,7 +16919,7 @@
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16887,7 +16945,7 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16913,7 +16971,7 @@
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16939,7 +16997,7 @@
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16965,7 +17023,7 @@
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -16991,7 +17049,7 @@
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17017,7 +17075,7 @@
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17043,7 +17101,7 @@
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17069,7 +17127,7 @@
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17095,7 +17153,7 @@
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17121,7 +17179,7 @@
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17147,7 +17205,7 @@
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17231,7 @@
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17199,7 +17257,7 @@
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17283,7 @@
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17251,7 +17309,7 @@
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17277,7 +17335,7 @@
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17303,7 +17361,7 @@
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17329,7 +17387,7 @@
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17355,7 +17413,7 @@
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17381,7 +17439,7 @@
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17407,7 +17465,7 @@
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17433,7 +17491,7 @@
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17459,7 +17517,7 @@
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17485,7 +17543,7 @@
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17511,7 +17569,7 @@
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17537,7 +17595,7 @@
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17563,7 +17621,7 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17589,7 +17647,7 @@
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17615,7 +17673,7 @@
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17641,7 +17699,7 @@
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17667,7 +17725,7 @@
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17693,7 +17751,7 @@
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17719,7 +17777,7 @@
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17745,7 +17803,7 @@
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17771,7 +17829,7 @@
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17797,7 +17855,7 @@
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17823,7 +17881,7 @@
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17849,7 +17907,7 @@
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17875,7 +17933,7 @@
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17901,7 +17959,7 @@
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17927,7 +17985,7 @@
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17953,7 +18011,7 @@
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -17979,7 +18037,7 @@
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18005,7 +18063,7 @@
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18031,7 +18089,7 @@
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18057,7 +18115,7 @@
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18083,7 +18141,7 @@
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18109,7 +18167,7 @@
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18135,7 +18193,7 @@
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18161,7 +18219,7 @@
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18187,7 +18245,7 @@
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18213,7 +18271,7 @@
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18239,7 +18297,7 @@
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18265,7 +18323,7 @@
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18291,7 +18349,7 @@
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18317,7 +18375,7 @@
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18343,7 +18401,7 @@
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18369,7 +18427,7 @@
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18395,7 +18453,7 @@
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18421,7 +18479,7 @@
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18447,7 +18505,7 @@
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18473,7 +18531,7 @@
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18499,7 +18557,7 @@
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18525,7 +18583,7 @@
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18551,7 +18609,7 @@
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18577,7 +18635,7 @@
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18603,7 +18661,7 @@
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18629,7 +18687,7 @@
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18655,7 +18713,7 @@
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18681,7 +18739,7 @@
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18707,7 +18765,7 @@
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18733,7 +18791,7 @@
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18759,7 +18817,7 @@
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18785,7 +18843,7 @@
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18811,7 +18869,7 @@
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18837,7 +18895,7 @@
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18863,7 +18921,7 @@
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18947,7 @@
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18915,7 +18973,7 @@
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18941,7 +18999,7 @@
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18967,7 +19025,7 @@
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -18993,7 +19051,7 @@
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19019,7 +19077,7 @@
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19045,7 +19103,7 @@
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19071,7 +19129,7 @@
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19097,7 +19155,7 @@
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19123,7 +19181,7 @@
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19149,7 +19207,7 @@
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19175,7 +19233,7 @@
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19201,7 +19259,7 @@
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19227,7 +19285,7 @@
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19253,7 +19311,7 @@
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19279,7 +19337,7 @@
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19305,7 +19363,7 @@
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19331,7 +19389,7 @@
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19357,7 +19415,7 @@
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19383,7 +19441,7 @@
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19409,7 +19467,7 @@
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19435,7 +19493,7 @@
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19461,7 +19519,7 @@
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19487,7 +19545,7 @@
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19513,7 +19571,7 @@
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19539,7 +19597,7 @@
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19565,7 +19623,7 @@
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19591,7 +19649,7 @@
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19617,7 +19675,7 @@
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19643,7 +19701,7 @@
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19669,7 +19727,7 @@
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19695,7 +19753,7 @@
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19721,7 +19779,7 @@
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19747,7 +19805,7 @@
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19773,7 +19831,7 @@
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19799,7 +19857,7 @@
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19825,7 +19883,7 @@
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19851,7 +19909,7 @@
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19877,7 +19935,7 @@
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19903,7 +19961,7 @@
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19929,7 +19987,7 @@
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19955,7 +20013,7 @@
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -19981,7 +20039,7 @@
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20007,7 +20065,7 @@
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20033,7 +20091,7 @@
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20059,7 +20117,7 @@
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20085,7 +20143,7 @@
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20111,7 +20169,7 @@
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20137,7 +20195,7 @@
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20163,7 +20221,7 @@
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20189,7 +20247,7 @@
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20215,7 +20273,7 @@
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20241,7 +20299,7 @@
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20267,7 +20325,7 @@
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20351,7 @@
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20319,7 +20377,7 @@
       </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20345,7 +20403,7 @@
       </c>
       <c r="F754" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20371,7 +20429,7 @@
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20397,7 +20455,7 @@
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20423,7 +20481,7 @@
       </c>
       <c r="F757" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20449,7 +20507,7 @@
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20475,7 +20533,7 @@
       </c>
       <c r="F759" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20501,7 +20559,7 @@
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20527,7 +20585,7 @@
       </c>
       <c r="F761" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20553,7 +20611,7 @@
       </c>
       <c r="F762" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20579,7 +20637,7 @@
       </c>
       <c r="F763" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20605,7 +20663,7 @@
       </c>
       <c r="F764" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20631,7 +20689,7 @@
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20657,7 +20715,7 @@
       </c>
       <c r="F766" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20683,7 +20741,7 @@
       </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20709,7 +20767,7 @@
       </c>
       <c r="F768" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20735,7 +20793,7 @@
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20761,7 +20819,7 @@
       </c>
       <c r="F770" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20787,7 +20845,7 @@
       </c>
       <c r="F771" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20813,7 +20871,7 @@
       </c>
       <c r="F772" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20839,7 +20897,7 @@
       </c>
       <c r="F773" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20865,7 +20923,7 @@
       </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20891,7 +20949,7 @@
       </c>
       <c r="F775" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20917,7 +20975,7 @@
       </c>
       <c r="F776" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20943,7 +21001,7 @@
       </c>
       <c r="F777" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20969,7 +21027,7 @@
       </c>
       <c r="F778" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -20995,7 +21053,7 @@
       </c>
       <c r="F779" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -21021,7 +21079,7 @@
       </c>
       <c r="F780" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -21047,7 +21105,7 @@
       </c>
       <c r="F781" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -21073,7 +21131,7 @@
       </c>
       <c r="F782" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -21099,7 +21157,7 @@
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -21125,7 +21183,7 @@
       </c>
       <c r="F784" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -21151,7 +21209,7 @@
       </c>
       <c r="F785" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -21177,7 +21235,7 @@
       </c>
       <c r="F786" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -21203,7 +21261,7 @@
       </c>
       <c r="F787" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -21229,7 +21287,7 @@
       </c>
       <c r="F788" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -21255,7 +21313,7 @@
       </c>
       <c r="F789" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -21281,7 +21339,7 @@
       </c>
       <c r="F790" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -21307,7 +21365,7 @@
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -21333,7 +21391,7 @@
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -21359,7 +21417,7 @@
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -21385,7 +21443,7 @@
       </c>
       <c r="F794" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -21411,7 +21469,7 @@
       </c>
       <c r="F795" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -21437,7 +21495,7 @@
       </c>
       <c r="F796" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -21463,7 +21521,7 @@
       </c>
       <c r="F797" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -21489,7 +21547,7 @@
       </c>
       <c r="F798" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -21515,7 +21573,7 @@
       </c>
       <c r="F799" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -21539,7 +21597,7 @@
       <c r="E800" t="inlineStr"/>
       <c r="F800" t="inlineStr">
         <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -22094,7 +22152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22140,25 +22198,35 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>n_process_time_blocks</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>bootstrap_unit</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>alarm_threshold</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>acceptance_target</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>claim_scope</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>calibration_id</t>
         </is>
@@ -22192,28 +22260,36 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.03751186708860758</v>
       </c>
       <c r="H2" t="n">
         <v>76</v>
       </c>
       <c r="I2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>3</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0.1</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>equal change contributes to conditional FAR; unequal and opposite changes are positive asymmetry stress tests and never enter FAR</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -22242,27 +22318,35 @@
         <v>0.7763157894736842</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6710526315789473</v>
+        <v>0.6811594202898551</v>
       </c>
       <c r="G3" t="n">
-        <v>0.868421052631579</v>
+        <v>0.8594096123417722</v>
       </c>
       <c r="H3" t="n">
         <v>76</v>
       </c>
       <c r="I3" t="n">
+        <v>11</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>3</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
         <is>
           <t>equal change contributes to conditional FAR; unequal and opposite changes are positive asymmetry stress tests and never enter FAR</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
@@ -22300,18 +22384,26 @@
         <v>76</v>
       </c>
       <c r="I4" t="n">
+        <v>11</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>3</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
         <is>
           <t>equal change contributes to conditional FAR; unequal and opposite changes are positive asymmetry stress tests and never enter FAR</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>D4CAL-V15-f6c351de01b0</t>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
         </is>
       </c>
     </row>
